--- a/reports/올리브영_시딩_성과보고서.xlsx
+++ b/reports/올리브영_시딩_성과보고서.xlsx
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -252,6 +252,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -644,7 +647,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>집계 26.09.04 · 시딩 2,139건 · 청구 931,288,075원 · 조회수 51,873,648 · 매출 1,420,018,525원</t>
+          <t>집계 26.09.07 · 시딩 2,139건 · 청구 930,344,264원(확정) · 조회수 56,612,765 · 매출 1,420,018,525원</t>
         </is>
       </c>
     </row>
@@ -680,7 +683,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>931288075</v>
+        <v>930344264</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -688,7 +691,7 @@
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>51873648</v>
+        <v>56612765</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -706,7 +709,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>488708205</v>
+        <v>492408205</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -758,7 +761,7 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>238394</v>
+        <v>240199</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -797,7 +800,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>9.4원 / 1,334원</t>
+          <t>9.5원 / 1,345원</t>
         </is>
       </c>
     </row>
@@ -869,7 +872,7 @@
         <v/>
       </c>
       <c r="D13" s="13" t="n">
-        <v>869492075</v>
+        <v>868548264</v>
       </c>
       <c r="E13" s="14">
         <f>D13/$D$16</f>
@@ -955,7 +958,9 @@
         <f>IFERROR(D15/B15,"")</f>
         <v/>
       </c>
-      <c r="G15" s="13" t="n"/>
+      <c r="G15" s="13" t="n">
+        <v>4739117</v>
+      </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
           <t>25.08</t>
@@ -963,7 +968,7 @@
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>바이오힐보 US · 성과 데이터 없음</t>
+          <t>바이오힐보 US · 조회수는 성과 확보 36건분</t>
         </is>
       </c>
     </row>
@@ -1004,21 +1009,21 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>진행 기준 총계 · 세금계산서 발행분 931,288,075 + JP 미발행 8,904,000</t>
+          <t>진행 기준 총계 · 세금계산서 발행분 930,344,264(확정) + JP 미발행 8,904,000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>[모수] 건수·비용 = 전체 2,139건 / 조회수·참여 기반 지표 = 조회수 집계분 2,050건 (글로벌 89건은 조회수 미집계)</t>
+          <t>[모수] 건수·비용 = 전체 2,139건 / 조회수·참여 = 성과 집계분 2,086건 / CPV·CPE = 원고료 집계분 2,050건 (05_기준정의 참조)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>[금액] 세금계산서 발행 총액 931,288,075원 기준 · 건당 청구단가 307,481원은 진행 건수가 확정된 1,770건 가중평균 (05_기준정의 참조)</t>
+          <t>[금액] 세금계산서 발행 총액 930,344,264원(26.09.07 확정) 기준 · 건당 청구단가 307,481원은 진행 건수가 확정된 1,770건 가중평균</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1074,7 +1079,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>수량 = 전체 2,139건 기준 / 성과 = 조회수 집계분 2,050건 기준</t>
+          <t>수량 = 전체 2,139건 기준 / 성과 = 성과 집계분 2,086건 기준 (바이오힐보 국내·해외 분리)</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1192,7 @@
         <v/>
       </c>
       <c r="E6" s="13" t="n">
-        <v>333750000</v>
+        <v>262375000</v>
       </c>
       <c r="F6" s="13">
         <f>IFERROR(E6/D6,"")</f>
@@ -1209,7 +1214,11 @@
         <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>2월 계상 71,375,000 확정 제외</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -1302,125 +1311,129 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>바이오힐보</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>바이오힐보 (국내)</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
         <v>195</v>
       </c>
-      <c r="C9" s="27" t="n">
-        <v>75</v>
-      </c>
-      <c r="D9" s="27">
+      <c r="C9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
         <f>SUM(B9:C9)</f>
         <v/>
       </c>
-      <c r="E9" s="27" t="n">
-        <v>36687500</v>
-      </c>
-      <c r="F9" s="27">
+      <c r="E9" s="13" t="n">
+        <v>6687500</v>
+      </c>
+      <c r="F9" s="13">
         <f>IFERROR(E9/D9,"")</f>
         <v/>
       </c>
-      <c r="G9" s="27" t="n">
-        <v>5484319</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>0.00455</v>
-      </c>
-      <c r="I9" s="27" t="n">
+      <c r="G9" s="13" t="n">
+        <v>5440064</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.004581</v>
+      </c>
+      <c r="I9" s="13" t="n">
         <v>56333229</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="13" t="n">
         <v>172219558</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="25">
         <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>글로벌 = US 68 + JP 7</t>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>국내 195건</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>식물나라</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="C10" s="13" t="n">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>바이오힐보 (해외·JP)</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="13">
+      <c r="C10" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="27">
         <f>SUM(B10:C10)</f>
         <v/>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>170441825</v>
-      </c>
-      <c r="F10" s="13">
+      <c r="E10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="27">
         <f>IFERROR(E10/D10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="13" t="n">
-        <v>2788821</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>0.007286</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>14985030</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>118255596</v>
-      </c>
-      <c r="K10" s="25">
+      <c r="G10" s="27" t="n">
+        <v>44255</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>0.000655</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="29">
         <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="inlineStr"/>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>26.06 JP 나노 7건 · 웨이크메이크 청구에 포함</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>웨이크메이크</t>
+          <t>바이오힐보 (해외·US)</t>
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D11" s="27">
         <f>SUM(B11:C11)</f>
         <v/>
       </c>
       <c r="E11" s="27" t="n">
-        <v>22067500</v>
+        <v>30000000</v>
       </c>
       <c r="F11" s="27">
         <f>IFERROR(E11/D11,"")</f>
         <v/>
       </c>
       <c r="G11" s="27" t="n">
-        <v>3143931</v>
+        <v>4739117</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>0.005756</v>
+        <v>0.005093</v>
       </c>
       <c r="I11" s="27" t="n">
-        <v>16409851</v>
+        <v>0</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>113788050</v>
+        <v>0</v>
       </c>
       <c r="K11" s="29">
         <f>IFERROR(J11/I11,"")</f>
@@ -1428,18 +1441,18 @@
       </c>
       <c r="L11" s="30" t="inlineStr">
         <is>
-          <t>JP 미발행 8,904,000 별도</t>
+          <t>25.08 US 68건 중 36건 성과 확보</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>루테카</t>
+          <t>식물나라</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>0</v>
@@ -1449,68 +1462,64 @@
         <v/>
       </c>
       <c r="E12" s="13" t="n">
-        <v>122312500</v>
+        <v>170441825</v>
       </c>
       <c r="F12" s="13">
         <f>IFERROR(E12/D12,"")</f>
         <v/>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1655285</v>
+        <v>2788821</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>0.005705</v>
+        <v>0.007286</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0</v>
+        <v>14985030</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>0</v>
+        <v>118255596</v>
       </c>
       <c r="K12" s="25">
         <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>광고 미집행 · 금액 71,375,000 미설명(A4)</t>
-        </is>
-      </c>
+      <c r="L12" s="16" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>컬러그램</t>
+          <t>웨이크메이크</t>
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D13" s="27">
         <f>SUM(B13:C13)</f>
         <v/>
       </c>
       <c r="E13" s="27" t="n">
-        <v>20225000</v>
+        <v>22067500</v>
       </c>
       <c r="F13" s="27">
         <f>IFERROR(E13/D13,"")</f>
         <v/>
       </c>
       <c r="G13" s="27" t="n">
-        <v>1583237</v>
+        <v>3143931</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>0.005376</v>
+        <v>0.005756</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>7670607</v>
+        <v>16409851</v>
       </c>
       <c r="J13" s="27" t="n">
-        <v>61405809</v>
+        <v>113788050</v>
       </c>
       <c r="K13" s="29">
         <f>IFERROR(J13/I13,"")</f>
@@ -1518,18 +1527,18 @@
       </c>
       <c r="L13" s="30" t="inlineStr">
         <is>
-          <t>ROAS 2위</t>
+          <t>JP 미발행 8,904,000 별도</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>케어플러스</t>
+          <t>루테카</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>0</v>
@@ -1539,17 +1548,17 @@
         <v/>
       </c>
       <c r="E14" s="13" t="n">
-        <v>8998750</v>
+        <v>122312500</v>
       </c>
       <c r="F14" s="13">
         <f>IFERROR(E14/D14,"")</f>
         <v/>
       </c>
       <c r="G14" s="13" t="n">
-        <v>188488</v>
+        <v>1655285</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>0.009757</v>
+        <v>0.005705</v>
       </c>
       <c r="I14" s="13" t="n">
         <v>0</v>
@@ -1563,63 +1572,63 @@
       </c>
       <c r="L14" s="16" t="inlineStr">
         <is>
-          <t>26.07 신규 · 광고 미집행</t>
+          <t>광고 미집행 · 브랜드 fade out</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>필리밀리</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>컬러그램</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D15" s="27">
         <f>SUM(B15:C15)</f>
         <v/>
       </c>
-      <c r="E15" s="13" t="n">
-        <v>3462500</v>
-      </c>
-      <c r="F15" s="13">
+      <c r="E15" s="27" t="n">
+        <v>20225000</v>
+      </c>
+      <c r="F15" s="27">
         <f>IFERROR(E15/D15,"")</f>
         <v/>
       </c>
-      <c r="G15" s="13" t="n">
-        <v>1353401</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>0.001453</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>14086284</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>121998372</v>
-      </c>
-      <c r="K15" s="25">
+      <c r="G15" s="27" t="n">
+        <v>1583237</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>0.005376</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>7670607</v>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>61405809</v>
+      </c>
+      <c r="K15" s="29">
         <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>ROAS 1위 · CPA 최저</t>
+      <c r="L15" s="30" t="inlineStr">
+        <is>
+          <t>ROAS 2위</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>케어플러스</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>0</v>
@@ -1629,17 +1638,17 @@
         <v/>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0</v>
+        <v>8998750</v>
       </c>
       <c r="F16" s="13">
         <f>IFERROR(E16/D16,"")</f>
         <v/>
       </c>
       <c r="G16" s="13" t="n">
-        <v>396952</v>
+        <v>188488</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>0.008666</v>
+        <v>0.009757</v>
       </c>
       <c r="I16" s="13" t="n">
         <v>0</v>
@@ -1653,156 +1662,558 @@
       </c>
       <c r="L16" s="16" t="inlineStr">
         <is>
-          <t>아이디얼포맨 청구에 포함</t>
+          <t>26.07 신규 · 원고료 3,700,000 확인</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="B17" s="32">
-        <f>SUM(B6:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>SUM(C6:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>SUM(D6:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="32">
-        <f>SUM(E6:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>필리밀리</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13">
+        <f>SUM(B17:C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>3462500</v>
+      </c>
+      <c r="F17" s="13">
         <f>IFERROR(E17/D17,"")</f>
         <v/>
       </c>
-      <c r="G17" s="32">
-        <f>SUM(G6:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="33">
-        <f>IFERROR((51873648*0+0.007060),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="32">
-        <f>SUM(I6:I16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="32">
-        <f>SUM(J6:J16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="34">
+      <c r="G17" s="13" t="n">
+        <v>1353401</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.001453</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>14086284</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>121998372</v>
+      </c>
+      <c r="K17" s="25">
         <f>IFERROR(J17/I17,"")</f>
         <v/>
       </c>
-      <c r="L17" s="35" t="inlineStr">
-        <is>
-          <t>2026 발행분 + US</t>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>ROAS 1위 · CPA 최저</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <f>SUM(B18:C18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13">
+        <f>IFERROR(E18/D18,"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>396952</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.008666</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="25">
+        <f>IFERROR(J18/I18,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>아이디얼포맨 청구에 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="B19" s="32">
+        <f>SUM(B6:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="32">
+        <f>SUM(C6:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="32">
+        <f>SUM(D6:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="32">
+        <f>SUM(E6:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="32">
+        <f>IFERROR(E19/D19,"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="32">
+        <f>SUM(G6:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="33">
+        <f>IFERROR((56612765*0+0.006896),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="32">
+        <f>SUM(I6:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="32">
+        <f>SUM(J6:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="34">
+        <f>IFERROR(J19/I19,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="35" t="inlineStr">
+        <is>
+          <t>2026 발행분 + US</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>확정 조정</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n">
+        <v>70431189</v>
+      </c>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="13" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>3~8월 발행 확정액 − 기존 내역 차이 · 브랜드 귀속 확인필요 (A1·A4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
           <t>2025 시딩 계약</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n">
         <v>59830000</v>
       </c>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="25" t="n"/>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="16" t="inlineStr">
         <is>
           <t>25.04~26.01 진행 272건 · 브랜드 혼재 (A3 참조)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B19" s="18">
-        <f>B17</f>
-        <v/>
-      </c>
-      <c r="C19" s="18">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="D19" s="18">
-        <f>D17</f>
-        <v/>
-      </c>
-      <c r="E19" s="18">
-        <f>E17+E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="18">
-        <f>IFERROR(E19/D19,"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="18">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="H19" s="19">
-        <f>H17</f>
-        <v/>
-      </c>
-      <c r="I19" s="18">
-        <f>I17</f>
-        <v/>
-      </c>
-      <c r="J19" s="18">
-        <f>J17</f>
-        <v/>
-      </c>
-      <c r="K19" s="36">
-        <f>IFERROR(J19/I19,"")</f>
-        <v/>
-      </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>세금계산서 총액 931,288,075원과 일치</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="B22" s="18">
+        <f>B19</f>
+        <v/>
+      </c>
+      <c r="C22" s="18">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D22" s="18">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E22" s="18">
+        <f>E19+E20+E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="18">
+        <f>IFERROR(E22/D22,"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="18">
+        <f>G19</f>
+        <v/>
+      </c>
+      <c r="H22" s="19">
+        <f>H19</f>
+        <v/>
+      </c>
+      <c r="I22" s="18">
+        <f>I19</f>
+        <v/>
+      </c>
+      <c r="J22" s="18">
+        <f>J19</f>
+        <v/>
+      </c>
+      <c r="K22" s="36">
+        <f>IFERROR(J22/I22,"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>세금계산서 확정 총액 930,344,264원과 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>· 글로벌 = 일본(JP) 시딩 라인 99건 + 바이오힐보 US 68건. 그 외는 전량 국내.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>· 성과(조회수·광고비·매출)는 조회수 집계분 2,050건에서 발생. 글로벌 89건(US 68 · JP 26.09 21)은 성과 데이터 없음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>· 성과(조회수·참여)는 성과 집계분 2,086건에서 발생. 미집계 53건 = US 32 + JP 26.09 21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>· 바이오힐보 US 68건은 청구 30,000,000원 전액을 계상하고 조회수는 성과 확보 36건분(4,739,117뷰)만 넣었다. 건당 조회수는 국내의 4.7배.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>· 2025 시딩 계약 59,830,000원은 브랜드가 혼재되어 별도 행으로 표기했고, 수량은 IMD 반영분(53건)만 위 브랜드에 들어가 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>바이오힐보 국내 · 해외 성과 분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>시딩 건수</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>성과 확보</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>조회수</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>건당 조회수</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>좋아요</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>댓글</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>참여수</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>참여율</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>원고료 / 청구</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>CPV</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>국내 (KR)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>5440064</v>
+      </c>
+      <c r="E30" s="13">
+        <f>IFERROR(D30/C30,"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>22032</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>2890</v>
+      </c>
+      <c r="H30" s="13">
+        <f>F30+G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="14">
+        <f>IFERROR(H30/D30,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>37900000</v>
+      </c>
+      <c r="K30" s="13">
+        <f>IFERROR(J30/D30,"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>원고료 기준 · 최대 764,503뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>해외 · 일본 (JP)</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>44255</v>
+      </c>
+      <c r="E31" s="27">
+        <f>IFERROR(D31/C31,"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="27">
+        <f>F31+G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="28">
+        <f>IFERROR(H31/D31,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="27" t="n">
+        <v>1665965</v>
+      </c>
+      <c r="K31" s="27">
+        <f>IFERROR(J31/D31,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="30" t="inlineStr">
+        <is>
+          <t>26.06 나노 시딩 테스트 · 최대 11,572뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>해외 · 미국 (US)</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>68</v>
+      </c>
+      <c r="C32" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="D32" s="27" t="n">
+        <v>4739117</v>
+      </c>
+      <c r="E32" s="27">
+        <f>IFERROR(D32/C32,"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>23068</v>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>1066</v>
+      </c>
+      <c r="H32" s="27">
+        <f>F32+G32</f>
+        <v/>
+      </c>
+      <c r="I32" s="28">
+        <f>IFERROR(H32/D32,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="27" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="K32" s="27">
+        <f>IFERROR(J32/D32,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="30" t="inlineStr">
+        <is>
+          <t>25.08 빅빙세일 · 청구 기준 · 최대 2,954,129뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>SUM(B30:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="18">
+        <f>SUM(C30:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="18">
+        <f>SUM(D30:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="18">
+        <f>IFERROR(D33/C33,"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="18">
+        <f>SUM(F30:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="18">
+        <f>SUM(G30:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="18">
+        <f>SUM(H30:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="19">
+        <f>IFERROR(H33/D33,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="18">
+        <f>SUM(J30:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>해외 75건이 전체 조회수의 46.8% · CPV는 기준이 달라 합산하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>· 해외 75건(전체의 27.8%)이 바이오힐보 총 조회수 10,223,436뷰의 46.8%를 만들었다. 건당 조회수는 US 131,642뷰 vs 국내 27,898뷰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>· US는 원고료 데이터가 없어 청구액 30,000,000원으로 CPV를 계산했다(68건 전액 ÷ 36건 조회수 → 보수적). 국내·JP는 원고료 기준.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>· US·JP는 파트너십 광고를 집행하지 않아 ROAS·CPA가 없다. 광고 성과 172,219,558원은 전량 국내 195건에서 발생.</t>
         </is>
       </c>
     </row>
@@ -1825,7 +2236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2048,7 +2459,9 @@
         <f>SUM(F8:G8)</f>
         <v/>
       </c>
-      <c r="I8" s="13" t="n"/>
+      <c r="I8" s="13" t="n">
+        <v>4739117</v>
+      </c>
       <c r="J8" s="13" t="n"/>
       <c r="K8" s="13" t="n"/>
       <c r="L8" s="25">
@@ -2057,7 +2470,7 @@
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>2025 계약 77건 + 바이오힐보 US</t>
+          <t>2025 계약 77건 + 바이오힐보 US 68건</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2664,7 @@
         <v/>
       </c>
       <c r="F14" s="13" t="n">
-        <v>164125000</v>
+        <v>92750000</v>
       </c>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13">
@@ -2271,7 +2684,11 @@
         <f>IFERROR(K14/J14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>발행 확정 92,750,000</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -2289,7 +2706,7 @@
         <v/>
       </c>
       <c r="F15" s="13" t="n">
-        <v>46737500</v>
+        <v>88812500</v>
       </c>
       <c r="G15" s="13" t="n"/>
       <c r="H15" s="13">
@@ -2331,7 +2748,7 @@
         <v/>
       </c>
       <c r="F16" s="13" t="n">
-        <v>124330000</v>
+        <v>129388689</v>
       </c>
       <c r="G16" s="13" t="n"/>
       <c r="H16" s="13">
@@ -2369,7 +2786,7 @@
         <v/>
       </c>
       <c r="F17" s="13" t="n">
-        <v>98428075</v>
+        <v>120981325</v>
       </c>
       <c r="G17" s="13" t="n"/>
       <c r="H17" s="13">
@@ -2455,7 +2872,7 @@
         <v/>
       </c>
       <c r="F19" s="13" t="n">
-        <v>116593750</v>
+        <v>85597500</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>8715000</v>
@@ -2501,7 +2918,7 @@
         <v/>
       </c>
       <c r="F20" s="13" t="n">
-        <v>127903750</v>
+        <v>159644250</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>20750000</v>
@@ -2523,7 +2940,11 @@
         <f>IFERROR(K20/J20,"")</f>
         <v/>
       </c>
-      <c r="M20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>발행 확정 180,394,250</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -2613,28 +3034,35 @@
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>금액 940,192,075 = 발행분 931,288,075 + JP 미발행 8,904,000</t>
+          <t>금액 939,248,264 = 발행 확정 930,344,264 + JP 미발행 8,904,000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>· KR 금액 = 해당 월 세금계산서 총액 − 글로벌 금액. 글로벌 = JP 시딩 라인 고정비 + 바이오힐보 US.</t>
+          <t>· KR 금액 = 해당 월 세금계산서 확정 총액 − 글로벌 금액. 글로벌 = JP 시딩 라인 고정비 + 바이오힐보 US.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>· 축이 다르다: 수량·성과는 업로드/진행월, 금액은 세금계산서 발행월(진행월 + 1개월). 같은 행의 수량과 금액이 같은 캠페인이 아닐 수 있다.</t>
+          <t>· 26.02~08 월별 금액은 26.09.07 확정 총액표를 그대로 반영했다. 기존 내역 대비 차이는 A1 하단 참조.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>· 25.08 US 68건, 26.09 JP 21건은 성과 데이터가 없다.</t>
+          <t>· 축이 다르다: 수량·성과는 업로드/진행월, 금액은 세금계산서 발행월(진행월 + 1개월). 같은 행의 수량과 금액이 같은 캠페인이 아닐 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>· 25.08 US 68건 중 36건은 조회수 확보(4,739,117뷰), 나머지 32건과 26.09 JP 21건은 성과 데이터가 없다.</t>
         </is>
       </c>
     </row>
@@ -2657,7 +3085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2680,7 +3108,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>광고 성과는 조회수 집계분 2,050건 기준 · 분포 모수 2,050건</t>
+          <t>광고 성과는 원고료·광고 집계분 2,050건 기준 · 조회수 분포 모수 2,086건 (US 36건 포함)</t>
         </is>
       </c>
     </row>
@@ -2836,7 +3264,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>조회수 분포  —  상위 255건(12.4%)이 전체 조회수의 70.4%</t>
+          <t>조회수 분포  —  상위 263건(12.6%)이 전체 조회수의 72.7%</t>
         </is>
       </c>
     </row>
@@ -2873,14 +3301,14 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C12" s="14">
-        <f>IFERROR(B12/2050,"")</f>
+        <f>IFERROR(B12/2086,"")</f>
         <v/>
       </c>
       <c r="D12" s="13" t="n">
-        <v>4223705</v>
+        <v>8479730</v>
       </c>
       <c r="E12" s="13" t="n"/>
       <c r="F12" s="13" t="n"/>
@@ -2894,14 +3322,14 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="14">
-        <f>IFERROR(B13/2050,"")</f>
+        <f>IFERROR(B13/2086,"")</f>
         <v/>
       </c>
       <c r="D13" s="13" t="n">
-        <v>8372082</v>
+        <v>12628107</v>
       </c>
       <c r="E13" s="13" t="n"/>
       <c r="F13" s="13" t="n"/>
@@ -2915,14 +3343,14 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C14" s="14">
-        <f>IFERROR(B14/2050,"")</f>
+        <f>IFERROR(B14/2086,"")</f>
         <v/>
       </c>
       <c r="D14" s="13" t="n">
-        <v>30296912</v>
+        <v>34552937</v>
       </c>
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="13" t="n"/>
@@ -2936,14 +3364,14 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C15" s="14">
-        <f>IFERROR(B15/2050,"")</f>
+        <f>IFERROR(B15/2086,"")</f>
         <v/>
       </c>
       <c r="D15" s="13" t="n">
-        <v>36528445</v>
+        <v>41147532</v>
       </c>
       <c r="E15" s="13" t="n"/>
       <c r="F15" s="13" t="n"/>
@@ -2957,14 +3385,14 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="C16" s="14">
-        <f>IFERROR(B16/2050,"")</f>
+        <f>IFERROR(B16/2086,"")</f>
         <v/>
       </c>
       <c r="D16" s="13" t="n">
-        <v>47217923</v>
+        <v>51889180</v>
       </c>
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="13" t="n"/>
@@ -3325,16 +3753,16 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>브링그린</t>
+          <t>바이오힐보 US</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>845657</v>
+        <v>2954129</v>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
@@ -3363,16 +3791,16 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보</t>
+          <t>브링그린</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="D38" s="13" t="n">
-        <v>764503</v>
+        <v>845657</v>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
@@ -3401,16 +3829,16 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>브링그린</t>
+          <t>바이오힐보 US</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>759673</v>
+        <v>791961</v>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
@@ -3439,16 +3867,16 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>아이디얼포맨</t>
+          <t>바이오힐보 국내</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>746820</v>
+        <v>764503</v>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
@@ -3482,11 +3910,11 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>601748</v>
+        <v>759673</v>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
@@ -3516,6 +3944,13 @@
     </row>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>· 조회수 TOP1·TOP3은 바이오힐보 US 건이다. US 36건 평균 조회수 131,642뷰 = 국내 평균 27,898뷰의 4.7배.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>· 루테카(124건)·케어플러스(32건)·올더베러(8건)·라운드어라운드(281건 중 1건만)는 광고 집행이 거의 없어 소재 활용 여지가 남아 있다.</t>
         </is>
@@ -3534,7 +3969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3611,234 +4046,238 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>조회수 · 참여 기반</t>
+          <t>조회수 · 참여 · 분포</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>2,050건</t>
+          <t>2,086건</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>글로벌 89건은 조회수 데이터가 없어 판정 불가 → 분모에서 제외</t>
+          <t>IMD 2,050 + 바이오힐보 US 36 (성과 확보분) · 미집계 53건은 분모 제외</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>CPV · CPE · 건당 조회수 · 분포 비중</t>
+          <t>총 조회수 · 총 참여 · 조회수 분포 · 건당 조회수</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
+          <t>CPV · CPE</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>2,050건</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>원고료가 확정된 건만. US 36건은 원고료 미기재라 분자·분모 모두 제외</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>CPV 9.49원 · CPE 1,345원</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
           <t>광고 성과</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>2,050건 중 집행분</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>파트너십 457 + 영상가공 125 = 582 소재</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>ROAS · CPA · 매출</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>② 금액 정의</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>건당</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>세금계산서 총액 (발행분)</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>931288075</v>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>원고료 + 마크업 + VAT + 솔루션 + 지급대행</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>— 아래 참조</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  + JP 미발행 (26.09)</t>
+          <t>세금계산서 총액 (발행 확정)</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>8904000</v>
+        <v>930344264</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>웨이크메이크 21건 · 26.10 발행 예정</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr"/>
+          <t>26.02~08 확정 840,514,264 + 25년 발행 89,830,000 (US 30,000,000 + 2025계약 59,830,000)</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>— 아래 참조</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  = 진행 기준 총계</t>
+          <t xml:space="preserve">  (기존 집계 대비)</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>940192075</v>
-      </c>
-      <c r="C14" s="16" t="inlineStr"/>
+        <v>-943811</v>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>26.02 계상 71,375,000 제외 + 26.03~08 재확정 +70,431,189</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>크리에이터 원고료</t>
+          <t xml:space="preserve">  + JP 미발행 (26.09)</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>488708205</v>
+        <v>8904000</v>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>마크업·VAT 제외 · IMD 2,050건</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>238,394원</t>
-        </is>
-      </c>
+          <t>웨이크메이크 21건 · 26.10 발행 예정</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  = 진행 기준 총계</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>939248264</v>
+      </c>
+      <c r="C16" s="16" t="inlineStr"/>
+      <c r="D16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>크리에이터 원고료</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>492408205</v>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>마크업·VAT 제외 · IMD 2,050건 + 케어플러스 3,700,000</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>240,199원</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
           <t>비시딩 항목 (확인분)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B18" s="13" t="n">
         <v>32400000</v>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>지급대행 25,200,000 · 모션그래픽 5,000,000 · 솔루션 2,000,000 · 풀필먼트 200,000</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>③ 건당 청구단가 307,481원 — 산정 근거</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>청구액</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>건당</t>
         </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>아이디얼포맨 1~6월 진행</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>872</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>296750000</v>
-      </c>
-      <c r="D20" s="13">
-        <f>IFERROR(C20/B20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>루테카 1~2월 진행</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>174</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>50937500</v>
-      </c>
-      <c r="D21" s="13">
-        <f>IFERROR(C21/B21,"")</f>
-        <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>식물나라 2~7월 진행</t>
+          <t>아이디얼포맨 1~6월 진행</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>384</v>
+        <v>872</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>106723250</v>
+        <v>296750000</v>
       </c>
       <c r="D22" s="13">
         <f>IFERROR(C22/B22,"")</f>
@@ -3848,14 +4287,14 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>바이오힐보 US</t>
+          <t>루테카 1~2월 진행</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>30000000</v>
+        <v>50937500</v>
       </c>
       <c r="D23" s="13">
         <f>IFERROR(C23/B23,"")</f>
@@ -3865,14 +4304,14 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>2025 시딩 계약</t>
+          <t>식물나라 2~7월 진행</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>272</v>
+        <v>384</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>59830000</v>
+        <v>106723250</v>
       </c>
       <c r="D24" s="13">
         <f>IFERROR(C24/B24,"")</f>
@@ -3880,127 +4319,125 @@
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>바이오힐보 US</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="D25" s="13">
+        <f>IFERROR(C25/B25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>2025 시딩 계약</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>272</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>59830000</v>
+      </c>
+      <c r="D26" s="13">
+        <f>IFERROR(C26/B26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>가중평균</t>
         </is>
       </c>
-      <c r="B25" s="18">
-        <f>SUM(B20:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="18">
-        <f>SUM(C20:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="18">
-        <f>IFERROR(C25/B25,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>· 분자·분모가 같은 자료에서 함께 확정되는 항목만 사용 (전체 청구액의 58%, 진행 1,770건).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>· 검증 1 — 아포맨 대조표 296,750,000 + 지급대행 5,000,000 = 세금계산서 발행 2~7월 301,750,000 (일치).</t>
-        </is>
+      <c r="B27" s="18">
+        <f>SUM(B22:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="18">
+        <f>SUM(C22:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="18">
+        <f>IFERROR(C27/B27,"")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>· 검증 2 — 아포맨 원고료 272,248원 × 마크업 1.25 = 340,310원 = 실제 청구 단가 (일치).</t>
+          <t>· 분자·분모가 같은 자료에서 함께 확정되는 항목만 사용 (전체 청구액의 58%, 진행 1,770건).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
+          <t>· 검증 1 — 아포맨 대조표 296,750,000 + 지급대행 5,000,000 = 세금계산서 발행 2~7월 301,750,000 (일치).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>· 검증 2 — 아포맨 원고료 272,248원 × 마크업 1.25 = 340,310원 = 실제 청구 단가 (일치).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
           <t>· 총액 931,288,075 ÷ 2,139 = 435,385원은 건당 단가가 아니다. 분자에 비시딩 항목이 있고, 청구 대응 진행 건수(약 2,787건)가 분모보다 크다.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>④ 용어</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>용어</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>정의</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>CPV</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>크리에이터 원고료 ÷ 총 조회수</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>9.42원</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>CPE</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>크리에이터 원고료 ÷ 총 참여(좋아요+댓글 366,236)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>1,334원</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr"/>
+      <c r="D34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>ROAS</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>전환 매출 ÷ 광고비</t>
+          <t>크리에이터 원고료 492,408,205 ÷ 조회수(원고료 집계분 2,050건) 51,873,648</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>파트너십 544% / 합산 530%</t>
+          <t>9.49원</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr"/>
@@ -4008,17 +4445,17 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>CPA</t>
+          <t>CPE</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>광고비 ÷ 구매건수</t>
+          <t>크리에이터 원고료 492,408,205 ÷ 참여(좋아요+댓글 366,236)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>3,409원</t>
+          <t>1,345원</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr"/>
@@ -4026,30 +4463,66 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>전환 매출 ÷ 광고비</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>파트너십 544% / 합산 530%</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>광고비 ÷ 구매건수</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>3,409원</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
           <t>참여율</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>(좋아요 + 댓글) ÷ 조회수</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>출처 — 세금계산서 총액표(26.09.01) · 2025 시딩 정산표 · 브랜드별 월별 대조표 · 글로벌 시딩 진행 라인 · IMD 성과 통계 v8(26.09.04) 원본데이터 2,050행</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>(좋아요 + 댓글) ÷ 조회수 · 2,086건 기준</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>출처 — 세금계산서 월별 확정 총액표(26.09.07) · 2025 시딩 정산표 · 브랜드별 월별 대조표 · 글로벌 시딩 진행 라인 · IMD 성과 통계 v8(26.09.04) 2,050행 · IMD 바이오힐보 US(26.09.07) 36행 · 케어플러스 시딩현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>개인정산 정보(주민등록번호·계좌·주소)는 원장 시트에만 있으며 본 보고서에는 포함하지 않음</t>
         </is>
@@ -4068,7 +4541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4093,219 +4566,169 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>프로젝트 · 국가 · 발행월별 · 2026년</t>
+          <t>발행 확정 총액(26.09.07) 및 프로젝트별 내역 대조</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>① 2026년 발행 확정 총액  —  기준 자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>발행 확정 (26.09.07)</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>구분 없음</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>92750000</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>88812500</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>129388689</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>120981325</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>133875000</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>94312500</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>180394250</v>
+      </c>
+      <c r="J6" s="18">
+        <f>SUM(C6:I6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>② 프로젝트별 내역  —  참고 (합계는 ①이 우선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>프로젝트</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>국가</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>4월</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>5월</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>6월</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>8월</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>올영PB라이프 - 아이디얼포맨</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>71375000</v>
-      </c>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>74125000</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>32125000</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>16125000</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="J5" s="13">
-        <f>SUM(C5:I5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>올영PB라이프 - 식물나라</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>13080000</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>24303075</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>19250000</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>43408750</v>
-      </c>
-      <c r="I6" s="13" t="n">
-        <v>57900000</v>
-      </c>
-      <c r="J6" s="13">
-        <f>SUM(C6:I6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>올영PB뷰티 - 브링그린</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n">
-        <v>15625000</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>34875000</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="J7" s="13">
-        <f>SUM(C7:I7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>올영PB라이프 - 라운드어라운드</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n">
-        <v>4675000</v>
-      </c>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n">
-        <v>62687500</v>
-      </c>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13">
-        <f>SUM(C8:I8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>올영PB - 케어플러스</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n">
-        <v>8998750</v>
-      </c>
-      <c r="J9" s="13">
-        <f>SUM(C9:I9)</f>
-        <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>올영PB - 필리밀리</t>
+          <t>올영PB라이프 - 아이디얼포맨</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -4315,13 +4738,21 @@
       </c>
       <c r="C10" s="13" t="n"/>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
+      <c r="E10" s="13" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>74125000</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>32125000</v>
+      </c>
       <c r="H10" s="13" t="n">
-        <v>3462500</v>
-      </c>
-      <c r="I10" s="13" t="n"/>
+        <v>16125000</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>32000000</v>
+      </c>
       <c r="J10" s="13">
         <f>SUM(C10:I10)</f>
         <v/>
@@ -4330,24 +4761,32 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>올영PB - 웨이크메이크</t>
+          <t>올영PB라이프 - 식물나라</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>일본(JP)</t>
+          <t>국내</t>
         </is>
       </c>
       <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
+      <c r="D11" s="13" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>13080000</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>24303075</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>19250000</v>
+      </c>
       <c r="H11" s="13" t="n">
-        <v>12937500</v>
+        <v>43408750</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>9130000</v>
+        <v>57900000</v>
       </c>
       <c r="J11" s="13">
         <f>SUM(C11:I11)</f>
@@ -4357,24 +4796,28 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>올영PB - 컬러그램</t>
+          <t>올영PB뷰티 - 브링그린</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>일본(JP)</t>
+          <t>국내</t>
         </is>
       </c>
       <c r="C12" s="13" t="n"/>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
+      <c r="E12" s="13" t="n">
+        <v>3250000</v>
+      </c>
       <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
+      <c r="G12" s="13" t="n">
+        <v>15625000</v>
+      </c>
       <c r="H12" s="13" t="n">
-        <v>12000000</v>
+        <v>34875000</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>8225000</v>
+        <v>32400000</v>
       </c>
       <c r="J12" s="13">
         <f>SUM(C12:I12)</f>
@@ -4384,23 +4827,23 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>올영PB신성장 - 루테카</t>
+          <t>올영PB라이프 - 라운드어라운드</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>국내+US 혼재</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>92750000</v>
-      </c>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n"/>
       <c r="D13" s="13" t="n">
-        <v>29562500</v>
+        <v>4675000</v>
       </c>
       <c r="E13" s="13" t="n"/>
       <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
+      <c r="G13" s="13" t="n">
+        <v>62687500</v>
+      </c>
       <c r="H13" s="13" t="n"/>
       <c r="I13" s="13" t="n"/>
       <c r="J13" s="13">
@@ -4411,79 +4854,89 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>올영PB - 바이오힐보</t>
+          <t>올영PB - 케어플러스</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>국내+JP 혼재</t>
+          <t>국내</t>
         </is>
       </c>
       <c r="C14" s="13" t="n"/>
       <c r="D14" s="13" t="n"/>
       <c r="E14" s="13" t="n"/>
       <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n">
-        <v>4187500</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="I14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n">
+        <v>8998750</v>
+      </c>
       <c r="J14" s="13">
         <f>SUM(C14:I14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>2026년 합계</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="18">
-        <f>SUM(C5:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>SUM(D5:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="18">
-        <f>SUM(E5:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="18">
-        <f>SUM(F5:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="18">
-        <f>SUM(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="18">
-        <f>SUM(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="18">
-        <f>SUM(I5:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="18">
-        <f>SUM(J5:J14)</f>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>올영PB - 필리밀리</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n">
+        <v>3462500</v>
+      </c>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13">
+        <f>SUM(C15:I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>올영PB - 웨이크메이크</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>일본(JP)</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n">
+        <v>12937500</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>9130000</v>
+      </c>
+      <c r="J16" s="13">
+        <f>SUM(C16:I16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2025.08  바이오힐보 US (68건)</t>
+          <t>올영PB - 컬러그램</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>미국(US)</t>
+          <t>일본(JP)</t>
         </is>
       </c>
       <c r="C17" s="13" t="n"/>
@@ -4491,55 +4944,302 @@
       <c r="E17" s="13" t="n"/>
       <c r="F17" s="13" t="n"/>
       <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n">
-        <v>30000000</v>
+      <c r="H17" s="13" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>8225000</v>
+      </c>
+      <c r="J17" s="13">
+        <f>SUM(C17:I17)</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>25.04~26.01  2025 시딩 계약 (272건)</t>
+          <t>올영PB신성장 - 루테카</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
+          <t>국내+US 혼재</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>92750000</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>29562500</v>
+      </c>
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="13" t="n"/>
       <c r="H18" s="13" t="n"/>
       <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n">
+      <c r="J18" s="13">
+        <f>SUM(C18:I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>올영PB - 바이오힐보</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>국내+JP 혼재</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n">
+        <v>4187500</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13">
+        <f>SUM(C19:I19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>내역 소계</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="inlineStr"/>
+      <c r="C20" s="32">
+        <f>SUM(C10:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>SUM(D10:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="32">
+        <f>SUM(E10:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>SUM(F10:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="32">
+        <f>SUM(G10:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="32">
+        <f>SUM(H10:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="32">
+        <f>SUM(I10:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="32">
+        <f>SUM(J10:J19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>차이 (① − ②)</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>귀속 확인필요</t>
+        </is>
+      </c>
+      <c r="C21" s="18">
+        <f>C6-C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="18">
+        <f>D6-D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="18">
+        <f>E6-E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="18">
+        <f>F6-F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="18">
+        <f>G6-G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="18">
+        <f>H6-H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="18">
+        <f>I6-I20</f>
+        <v/>
+      </c>
+      <c r="J21" s="18">
+        <f>J6-J20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>③ 세금계산서 총 발행액</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr"/>
+      <c r="D24" s="11" t="inlineStr"/>
+      <c r="E24" s="11" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr"/>
+      <c r="G24" s="11" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr"/>
+      <c r="I24" s="11" t="inlineStr"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026.02~08 발행 확정</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>구분 없음</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13">
+        <f>J6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>2025.08  바이오힐보 US (68건)</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>미국(US)</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n">
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>25.04~26.01  2025 시딩 계약 (272건)</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n">
         <v>59830000</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>세금계산서 총액 (발행분)</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="n"/>
-      <c r="I19" s="18" t="n"/>
-      <c r="J19" s="18">
-        <f>J15+J17+J18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>세금계산서 총액 (발행 확정)</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18">
+        <f>J25+J26+J27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>· 26.02~08 금액은 26.09.07 확정 총액표 그대로다. 프로젝트별 내역(②)은 이전 집계 기준이며, 차이는 아직 프로젝트에 귀속되지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>· 확정 반영으로 빠진 것 — 26.02 아이디얼포맨 계상분 71,375,000원 (확정 2월 92,750,000원은 루테카 단독과 일치).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>· 확정 반영으로 더해진 것 — 26.03 +42,075,000 / 26.04 +5,058,689 / 26.05 +22,553,250 / 26.08 +31,740,500, 26.07 −30,996,250 (7→8월 발행 이동으로 추정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>· 순증감 −943,811원 (기존 집계 931,288,075 → 확정 930,344,264).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>· 총액표에 국가 구분이 없어 글로벌 시딩 라인 자료로 귀속했다. 루테카·바이오힐보는 분리 근거가 없어 혼재로 둔다.</t>
         </is>
@@ -6248,7 +6948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6268,7 +6968,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>자료 간 불일치 · 미확정 사항 12건</t>
+          <t>자료 간 불일치 · 미확정 사항 12건 (해결 3건 포함) · 26.09.07 갱신</t>
         </is>
       </c>
     </row>
@@ -6305,16 +7005,16 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>루테카 발행액 미설명</t>
+          <t>확정 조정액 브랜드 귀속</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>세금계산서 122,312,500 vs 진행 대조표 50,937,500 → 71,375,000 미설명. "올영PB신성장" 부문 타 항목 포함 여부 확인</t>
+          <t>26.03~08 발행 확정액이 기존 내역보다 70,431,189원 많다(03 +42,075,000 / 04 +5,058,689 / 05 +22,553,250 / 07 −30,996,250 / 08 +31,740,500). 프로젝트별 귀속 필요</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>71375000</v>
+        <v>70431189</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -6333,7 +7033,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>세금계산서에 수량 미기재 → 931,288,075원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
+          <t>세금계산서에 수량 미기재 → 930,344,264원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
@@ -6370,12 +7070,12 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보 비용 귀속</t>
+          <t>바이오힐보 국내 비용 귀속</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>IMD 202건·원고료 39,565,965인데 26년 발행액은 6,687,500뿐. 2025 계약 + US 30,000,000 + 브랜드사 직계약으로 분산 추정</t>
+          <t>국내 195건·원고료 37,900,000인데 26년 발행액은 6,687,500뿐. 2025 계약 + 브랜드사 직계약으로 분산 추정</t>
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
@@ -6546,25 +7246,138 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
+          <t>바이오힐보 US 미집계 32건</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>US 68건 중 36건만 성과 확보(4,739,117뷰). 나머지 32건 조회수·참여 데이터 미확보 → 실제 성과는 현재 수치 이상</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>바이오힐보 US 원고료</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>US 36건 원고료 미기재. 청구 30,000,000원만 확인되어 CPV는 청구 기준으로 산출(국내·JP와 기준 상이)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>케어플러스 청구 차이</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>협의 비용 합 7,825,000(+VAT 8,607,500) vs 세금계산서 8,998,750 → 391,250 차이</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>391250</v>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>해결</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>루테카 발행액 71,375,000</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>26.02 확정액이 92,750,000(루테카 단독)으로 확정되어 아이디얼포맨 2월 계상분 71,375,000은 제외 확정</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>해결</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
           <t>케어플러스 원고료</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>IMD 32건 원고료 0원(미입력). 세금계산서 발행액은 8,998,750</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>8998750</v>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>시딩현황에서 확인 — 마이크로 5건×200,000 + 나노 27건×100,000 = 3,700,000원. CPV 19.63원 / CPE 2,012원</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>해결</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>바이오힐보 US 성과</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>IMD 26.09.07로 36건 확보 — 4,739,117뷰 / 좋아요 23,068 / 댓글 1,066 / 최대 2,954,129뷰(전체 1위)</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>· 금액 영향은 미설명·수정 필요 금액의 절대값이며 서로 중복될 수 있어 합산하지 않는다.</t>
         </is>

--- a/reports/올리브영_시딩_성과보고서.xlsx
+++ b/reports/올리브영_시딩_성과보고서.xlsx
@@ -647,7 +647,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>집계 26.09.07 · 시딩 2,139건 · 청구 930,344,264원(확정) · 조회수 56,612,765 · 매출 1,420,018,525원</t>
+          <t>집계 26.09.07 · 시딩 2,139건 · 청구 840,514,264원(확정) · 조회수 56,612,765 · 매출 1,420,018,525원</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>930344264</v>
+        <v>840514264</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="D13" s="13" t="n">
-        <v>868548264</v>
+        <v>778718264</v>
       </c>
       <c r="E13" s="14">
         <f>D13/$D$16</f>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>진행 기준 총계 · 세금계산서 발행분 930,344,264(확정) + JP 미발행 8,904,000</t>
+          <t>진행 기준 총계 · 세금계산서 발행 확정 840,514,264 + JP 미발행 8,904,000</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>[금액] 세금계산서 발행 총액 930,344,264원(26.09.07 확정) 기준 · 건당 청구단가 307,481원은 진행 건수가 확정된 1,770건 가중평균</t>
+          <t>[금액] 세금계산서 발행 총액 840,514,264원(26.09.07 확정 · 26.02~08 발행분이 전부이며 2025 진행분 정산·바이오힐보 US 포함) 기준</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       <c r="C20" s="13" t="n"/>
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="13" t="n">
-        <v>70431189</v>
+        <v>40431189</v>
       </c>
       <c r="F20" s="13" t="n"/>
       <c r="G20" s="13" t="n"/>
@@ -1828,7 +1828,7 @@
       <c r="K20" s="25" t="n"/>
       <c r="L20" s="16" t="inlineStr">
         <is>
-          <t>3~8월 발행 확정액 − 기존 내역 차이 · 브랜드 귀속 확인필요 (A1·A4)</t>
+          <t>발행 확정 총액 − 프로젝트별 내역 차이 · 브랜드 귀속 확인필요 (A1·A4)</t>
         </is>
       </c>
     </row>
@@ -1841,9 +1841,7 @@
       <c r="B21" s="13" t="n"/>
       <c r="C21" s="13" t="n"/>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n">
-        <v>59830000</v>
-      </c>
+      <c r="E21" s="13" t="n"/>
       <c r="F21" s="13" t="n"/>
       <c r="G21" s="13" t="n"/>
       <c r="H21" s="14" t="n"/>
@@ -1852,7 +1850,7 @@
       <c r="K21" s="25" t="n"/>
       <c r="L21" s="16" t="inlineStr">
         <is>
-          <t>25.04~26.01 진행 272건 · 브랜드 혼재 (A3 참조)</t>
+          <t>25.04~26.01 진행 272건 · 정산액은 위 확정 총액에 포함 (A3 참조)</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1873,7 @@
         <v/>
       </c>
       <c r="E22" s="18">
-        <f>E19+E20+E21</f>
+        <f>E19+E20</f>
         <v/>
       </c>
       <c r="F22" s="18">
@@ -1904,7 +1902,7 @@
       </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>세금계산서 확정 총액 930,344,264원과 일치</t>
+          <t>세금계산서 발행 확정 840,514,264원과 일치</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1930,7 @@
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>· 2025 시딩 계약 59,830,000원은 브랜드가 혼재되어 별도 행으로 표기했고, 수량은 IMD 반영분(53건)만 위 브랜드에 들어가 있다.</t>
+          <t>· 2025 시딩 계약(272건)의 정산액 59,830,000원은 26.02~08 발행 확정 총액 안에 포함되어 있어 별도 금액으로 더하지 않는다. 수량은 IMD 반영분(53건)만 위 브랜드에 들어가 있다.</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2379,9 +2377,7 @@
         <f>SUM(B6:D6)</f>
         <v/>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>7300000</v>
-      </c>
+      <c r="F6" s="13" t="n"/>
       <c r="G6" s="13" t="n"/>
       <c r="H6" s="13">
         <f>SUM(F6:G6)</f>
@@ -2396,7 +2392,7 @@
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>2025 계약 진행 (식물나라 51건)</t>
+          <t>2025 계약 진행 (식물나라 51건) · 정산은 26년 발행</t>
         </is>
       </c>
     </row>
@@ -2413,9 +2409,7 @@
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
-      <c r="F7" s="13" t="n">
-        <v>12215000</v>
-      </c>
+      <c r="F7" s="13" t="n"/>
       <c r="G7" s="13" t="n"/>
       <c r="H7" s="13">
         <f>SUM(F7:G7)</f>
@@ -2430,7 +2424,7 @@
       </c>
       <c r="M7" s="16" t="inlineStr">
         <is>
-          <t>2025 계약 진행 (44건)</t>
+          <t>2025 계약 진행 (44건) · 정산은 26년 발행</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2443,8 @@
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="13" t="n">
-        <v>19315000</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>30000000</v>
-      </c>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
       <c r="H8" s="13">
         <f>SUM(F8:G8)</f>
         <v/>
@@ -2470,7 +2460,7 @@
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>2025 계약 77건 + 바이오힐보 US 68건</t>
+          <t>2025 계약 77건 + 바이오힐보 US 68건 · 정산은 26년 발행</t>
         </is>
       </c>
     </row>
@@ -2525,9 +2515,7 @@
         <f>SUM(B10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="13" t="n">
-        <v>11760000</v>
-      </c>
+      <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="13">
         <f>SUM(F10:G10)</f>
@@ -2542,7 +2530,11 @@
         <f>IFERROR(K10/J10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>정산은 26년 발행</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -2559,9 +2551,7 @@
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="13" t="n">
-        <v>8190000</v>
-      </c>
+      <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
       <c r="H11" s="13">
         <f>SUM(F11:G11)</f>
@@ -2576,7 +2566,11 @@
         <f>IFERROR(K11/J11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>정산은 26년 발행</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -2625,9 +2619,7 @@
         <f>SUM(B13:D13)</f>
         <v/>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>1050000</v>
-      </c>
+      <c r="F13" s="13" t="n"/>
       <c r="G13" s="13" t="n"/>
       <c r="H13" s="13">
         <f>SUM(F13:G13)</f>
@@ -2646,7 +2638,11 @@
         <f>IFERROR(K13/J13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>정산은 26.02 이후 발행</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -2686,7 +2682,7 @@
       </c>
       <c r="M14" s="16" t="inlineStr">
         <is>
-          <t>발행 확정 92,750,000</t>
+          <t>발행 확정</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2848,11 @@
         <f>IFERROR(K18/J18,"")</f>
         <v/>
       </c>
-      <c r="M18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>발행 확정 133,875,000</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -2949,21 +2949,21 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026.09</t>
+          <t>(발행월 미확정)</t>
         </is>
       </c>
       <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n">
-        <v>21</v>
-      </c>
+      <c r="C21" s="13" t="n"/>
       <c r="D21" s="13" t="n"/>
       <c r="E21" s="13">
         <f>SUM(B21:D21)</f>
         <v/>
       </c>
-      <c r="F21" s="13" t="n"/>
+      <c r="F21" s="13" t="n">
+        <v>-30000000</v>
+      </c>
       <c r="G21" s="13" t="n">
-        <v>8904000</v>
+        <v>30000000</v>
       </c>
       <c r="H21" s="13">
         <f>SUM(F21:G21)</f>
@@ -2978,89 +2978,132 @@
       </c>
       <c r="M21" s="16" t="inlineStr">
         <is>
+          <t>바이오힐보 US 30,000,000 국가 재배분 (금액 총계 불변)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13">
+        <f>SUM(B22:D22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n">
+        <v>8904000</v>
+      </c>
+      <c r="H22" s="13">
+        <f>SUM(F22:G22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="13" t="n"/>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="25">
+        <f>IFERROR(K22/J22,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
           <t>JP 진행 · 세금계산서 미발행</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B22" s="18">
-        <f>SUM(B6:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="18">
-        <f>SUM(C6:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="18">
-        <f>SUM(D6:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="18">
-        <f>SUM(E6:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="18">
-        <f>SUM(F6:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="18">
-        <f>SUM(G6:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="18">
-        <f>SUM(H6:H21)</f>
-        <v/>
-      </c>
-      <c r="I22" s="18">
-        <f>SUM(I6:I21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="18">
-        <f>SUM(J6:J21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="18">
-        <f>SUM(K6:K21)</f>
-        <v/>
-      </c>
-      <c r="L22" s="36">
-        <f>IFERROR(K22/J22,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>금액 939,248,264 = 발행 확정 930,344,264 + JP 미발행 8,904,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>· KR 금액 = 해당 월 세금계산서 확정 총액 − 글로벌 금액. 글로벌 = JP 시딩 라인 고정비 + 바이오힐보 US.</t>
+      <c r="B23" s="18">
+        <f>SUM(B6:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="18">
+        <f>SUM(C6:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f>SUM(D6:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="18">
+        <f>SUM(E6:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="18">
+        <f>SUM(F6:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="18">
+        <f>SUM(G6:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="18">
+        <f>SUM(H6:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="18">
+        <f>SUM(I6:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="18">
+        <f>SUM(J6:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="18">
+        <f>SUM(K6:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="36">
+        <f>IFERROR(K23/J23,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>금액 849,418,264 = 발행 확정 840,514,264 + JP 미발행 8,904,000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>· 26.02~08 월별 금액은 26.09.07 확정 총액표를 그대로 반영했다. 기존 내역 대비 차이는 A1 하단 참조.</t>
+          <t>· KR 금액 = 해당 월 세금계산서 확정 총액 − 글로벌 금액. 글로벌 = JP 시딩 라인 고정비 + 바이오힐보 US.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>· 축이 다르다: 수량·성과는 업로드/진행월, 금액은 세금계산서 발행월(진행월 + 1개월). 같은 행의 수량과 금액이 같은 캠페인이 아닐 수 있다.</t>
+          <t>· 26.02~08 월별 금액은 26.09.07 확정 총액표를 그대로 반영했고, 이 7개월분이 세금계산서 발행액 전부다. 2025 진행분 정산·바이오힐보 US도 이 안에 포함된다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>· 바이오힐보 US 30,000,000원은 발행월이 특정되지 않아 국가 배분만 별도 행으로 조정했다(KR −30,000,000 / 글로벌 +30,000,000, 총계 불변).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>· 축이 다르다: 수량·성과는 업로드/진행월, 금액은 세금계산서 발행월(진행월 + 1개월). 같은 행의 수량과 금액이 같은 캠페인이 아닐 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>· 25.08 US 68건 중 36건은 조회수 확보(4,739,117뷰), 나머지 32건과 26.09 JP 21건은 성과 데이터가 없다.</t>
         </is>
@@ -4145,11 +4188,11 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>930344264</v>
+        <v>840514264</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>26.02~08 확정 840,514,264 + 25년 발행 89,830,000 (US 30,000,000 + 2025계약 59,830,000)</t>
+          <t>26.02~08 발행분이 전부. 2025 진행분 정산 59,830,000 · 바이오힐보 US 30,000,000도 이 안에 포함</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -4165,11 +4208,11 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-943811</v>
+        <v>-90773811</v>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>26.02 계상 71,375,000 제외 + 26.03~08 재확정 +70,431,189</t>
+          <t>기존 931,288,075은 25년 발행분 89,830,000을 별도로 더한 값 → 확정 총액에 이미 포함되어 있어 중복</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr"/>
@@ -4197,7 +4240,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>939248264</v>
+        <v>849418264</v>
       </c>
       <c r="C16" s="16" t="inlineStr"/>
       <c r="D16" s="16" t="inlineStr"/>
@@ -4374,7 +4417,7 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>· 분자·분모가 같은 자료에서 함께 확정되는 항목만 사용 (전체 청구액의 58%, 진행 1,770건).</t>
+          <t>· 분자·분모가 같은 자료에서 함께 확정되는 항목만 사용 (전체 청구액의 65%, 진행 1,770건).</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4438,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>· 총액 931,288,075 ÷ 2,139 = 435,385원은 건당 단가가 아니다. 분자에 비시딩 항목이 있고, 청구 대응 진행 건수(약 2,787건)가 분모보다 크다.</t>
+          <t>· 총액 840,514,264 ÷ 2,139 = 392,948원은 건당 단가가 아니다. 분자에 비시딩 항목이 있고, 청구 대응 진행 건수(약 2,787건)가 분모보다 크다.</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5096,7 +5139,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>③ 세금계산서 총 발행액</t>
+          <t>③ 세금계산서 총 발행액 · 국가 배분</t>
         </is>
       </c>
     </row>
@@ -5125,24 +5168,24 @@
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>2026.02~08 발행 확정</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>구분 없음</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="13" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>세금계산서 총액 (발행 확정)</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>26.02~08</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18">
         <f>J6</f>
         <v/>
       </c>
@@ -5150,12 +5193,12 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>2025.08  바이오힐보 US (68건)</t>
+          <t xml:space="preserve">  글로벌 · 일본(JP) 발행분</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>미국(US)</t>
+          <t>일본(JP)</t>
         </is>
       </c>
       <c r="C26" s="13" t="n"/>
@@ -5166,18 +5209,18 @@
       <c r="H26" s="13" t="n"/>
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="13" t="n">
-        <v>30000000</v>
+        <v>31796000</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>25.04~26.01  2025 시딩 계약 (272건)</t>
+          <t xml:space="preserve">  글로벌 · 바이오힐보 US</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>국내</t>
+          <t>미국(US)</t>
         </is>
       </c>
       <c r="C27" s="13" t="n"/>
@@ -5188,58 +5231,103 @@
       <c r="H27" s="13" t="n"/>
       <c r="I27" s="13" t="n"/>
       <c r="J27" s="13" t="n">
-        <v>59830000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>세금계산서 총액 (발행 확정)</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="18" t="n"/>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="18">
-        <f>J25+J26+J27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>· 26.02~08 금액은 26.09.07 확정 총액표 그대로다. 프로젝트별 내역(②)은 이전 집계 기준이며, 차이는 아직 프로젝트에 귀속되지 않았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>· 확정 반영으로 빠진 것 — 26.02 아이디얼포맨 계상분 71,375,000원 (확정 2월 92,750,000원은 루테카 단독과 일치).</t>
-        </is>
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  국내 (KR) = 총액 − 글로벌</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="32" t="n"/>
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="32" t="n"/>
+      <c r="H28" s="32" t="n"/>
+      <c r="I28" s="32" t="n"/>
+      <c r="J28" s="32">
+        <f>J25-J26-J27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + JP 미발행 (26.09)</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>일본(JP)</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="13" t="n">
+        <v>8904000</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>진행 기준 총계</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18">
+        <f>J25+J29</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>· 확정 반영으로 더해진 것 — 26.03 +42,075,000 / 26.04 +5,058,689 / 26.05 +22,553,250 / 26.08 +31,740,500, 26.07 −30,996,250 (7→8월 발행 이동으로 추정).</t>
+          <t>· 26.02~08 확정 총액 840,514,264원이 세금계산서 발행액 전부다. 2025 진행분 정산(59,830,000)과 바이오힐보 US(30,000,000)도 이 안에 포함되어 있어 별도로 더하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>· 순증감 −943,811원 (기존 집계 931,288,075 → 확정 930,344,264).</t>
+          <t>· 기존 집계 931,288,075원은 위 두 항목을 확정 총액에 다시 더한 값이었다 (중복 89,830,000). 정정 후 −90,773,811원.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>· 확정 반영으로 빠진 것 — 26.02 아이디얼포맨 계상분 71,375,000원 (확정 2월 92,750,000원은 루테카 단독과 일치).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>· 프로젝트별 내역(②) 대비 차액 70,431,189원 — 2025 계약 정산분·US 청구분(합 89,830,000)의 일부가 여기에, 나머지는 이미 ②의 프로젝트 라인에 계상된 것으로 보인다. 정확한 귀속은 확인 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>· 총액표에 국가 구분이 없어 글로벌 시딩 라인 자료로 귀속했다. 루테카·바이오힐보는 분리 근거가 없어 혼재로 둔다.</t>
         </is>
@@ -7010,7 +7098,7 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>26.03~08 발행 확정액이 기존 내역보다 70,431,189원 많다(03 +42,075,000 / 04 +5,058,689 / 05 +22,553,250 / 07 −30,996,250 / 08 +31,740,500). 프로젝트별 귀속 필요</t>
+          <t>발행 확정 총액이 프로젝트별 내역보다 70,431,189원 많다(US 30,000,000 제외 시 40,431,189). 2025 계약 정산분·US 청구분 포함 여부와 프로젝트별 귀속 확인 필요</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
@@ -7033,7 +7121,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>세금계산서에 수량 미기재 → 930,344,264원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
+          <t>세금계산서에 수량 미기재 → 840,514,264원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
         </is>
       </c>
       <c r="D6" s="13" t="n"/>

--- a/reports/올리브영_시딩_성과보고서.xlsx
+++ b/reports/올리브영_시딩_성과보고서.xlsx
@@ -647,7 +647,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>집계 26.09.07 · 시딩 2,139건 · 청구 840,514,264원(확정) · 조회수 56,612,765 · 매출 1,420,018,525원</t>
+          <t>집계 26.09.07 · 시딩 2,139건 · 청구 900,344,264원(확정) · 조회수 56,612,765 · 매출 1,420,018,525원</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>840514264</v>
+        <v>900344264</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>307481</v>
+        <v>290531</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="D13" s="13" t="n">
-        <v>778718264</v>
+        <v>838548264</v>
       </c>
       <c r="E13" s="14">
         <f>D13/$D$16</f>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>진행 기준 총계 · 세금계산서 발행 확정 840,514,264 + JP 미발행 8,904,000</t>
+          <t>진행 기준 총계 · 발행 확정 900,344,264 (26년 840,514,264 + 25년 59,830,000) + JP 미발행 8,904,000</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>[금액] 세금계산서 발행 총액 840,514,264원(26.09.07 확정 · 26.02~08 발행분이 전부이며 2025 진행분 정산·바이오힐보 US 포함) 기준</t>
+          <t>[금액] 세금계산서 발행 총액 900,344,264원 = 26.02~08 확정 840,514,264 + 25년 발행 59,830,000(바이오힐보 US 30,000,000 포함)</t>
         </is>
       </c>
     </row>
@@ -1416,9 +1416,7 @@
         <f>SUM(B11:C11)</f>
         <v/>
       </c>
-      <c r="E11" s="27" t="n">
-        <v>30000000</v>
-      </c>
+      <c r="E11" s="27" t="n"/>
       <c r="F11" s="27">
         <f>IFERROR(E11/D11,"")</f>
         <v/>
@@ -1441,7 +1439,7 @@
       </c>
       <c r="L11" s="30" t="inlineStr">
         <is>
-          <t>25.08 US 68건 중 36건 성과 확보</t>
+          <t>25.08 US 68건 중 36건 성과 확보 · 청구 30,000,000은 2025 계약 정산분에 포함</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1816,7 @@
       <c r="C20" s="13" t="n"/>
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="13" t="n">
-        <v>40431189</v>
+        <v>70431189</v>
       </c>
       <c r="F20" s="13" t="n"/>
       <c r="G20" s="13" t="n"/>
@@ -1828,7 +1826,7 @@
       <c r="K20" s="25" t="n"/>
       <c r="L20" s="16" t="inlineStr">
         <is>
-          <t>발행 확정 총액 − 프로젝트별 내역 차이 · 브랜드 귀속 확인필요 (A1·A4)</t>
+          <t>26.02~08 발행 확정액 − 프로젝트별 내역 차이 · 브랜드 귀속 확인필요 (A1·A4)</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1839,9 @@
       <c r="B21" s="13" t="n"/>
       <c r="C21" s="13" t="n"/>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
+      <c r="E21" s="13" t="n">
+        <v>59830000</v>
+      </c>
       <c r="F21" s="13" t="n"/>
       <c r="G21" s="13" t="n"/>
       <c r="H21" s="14" t="n"/>
@@ -1850,7 +1850,7 @@
       <c r="K21" s="25" t="n"/>
       <c r="L21" s="16" t="inlineStr">
         <is>
-          <t>25.04~26.01 진행 272건 · 정산액은 위 확정 총액에 포함 (A3 참조)</t>
+          <t>25.04~26.01 진행 272건 · 바이오힐보 US 30,000,000 포함 · 브랜드 혼재 (A3 참조)</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         <v/>
       </c>
       <c r="E22" s="18">
-        <f>E19+E20</f>
+        <f>E19+E20+E21</f>
         <v/>
       </c>
       <c r="F22" s="18">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>세금계산서 발행 확정 840,514,264원과 일치</t>
+          <t>세금계산서 발행 확정 900,344,264원과 일치</t>
         </is>
       </c>
     </row>
@@ -1923,14 +1923,14 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>· 바이오힐보 US 68건은 청구 30,000,000원 전액을 계상하고 조회수는 성과 확보 36건분(4,739,117뷰)만 넣었다. 건당 조회수는 국내의 4.7배.</t>
+          <t>· 바이오힐보 US 68건의 청구 30,000,000원은 2025 시딩 계약 행에 포함돼 있다. 조회수는 성과 확보 36건분(4,739,117뷰)이며 건당 조회수는 국내의 4.7배.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>· 2025 시딩 계약(272건)의 정산액 59,830,000원은 26.02~08 발행 확정 총액 안에 포함되어 있어 별도 금액으로 더하지 않는다. 수량은 IMD 반영분(53건)만 위 브랜드에 들어가 있다.</t>
+          <t>· 2025 시딩 계약 정산액 59,830,000원에는 바이오힐보 US 30,000,000원이 포함되어 있다. 따라서 US 행의 청구 금액은 비웠고, 수량은 IMD 반영분(53건)만 위 브랜드에 들어가 있다.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,9 @@
         <f>SUM(B6:D6)</f>
         <v/>
       </c>
-      <c r="F6" s="13" t="n"/>
+      <c r="F6" s="13" t="n">
+        <v>7300000</v>
+      </c>
       <c r="G6" s="13" t="n"/>
       <c r="H6" s="13">
         <f>SUM(F6:G6)</f>
@@ -2392,7 +2394,7 @@
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>2025 계약 진행 (식물나라 51건) · 정산은 26년 발행</t>
+          <t>2025 계약 진행 (식물나라 51건)</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2411,9 @@
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
-      <c r="F7" s="13" t="n"/>
+      <c r="F7" s="13" t="n">
+        <v>12215000</v>
+      </c>
       <c r="G7" s="13" t="n"/>
       <c r="H7" s="13">
         <f>SUM(F7:G7)</f>
@@ -2424,7 +2428,7 @@
       </c>
       <c r="M7" s="16" t="inlineStr">
         <is>
-          <t>2025 계약 진행 (44건) · 정산은 26년 발행</t>
+          <t>2025 계약 진행 (44건)</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2447,9 @@
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="13" t="n"/>
+      <c r="F8" s="13" t="n">
+        <v>19315000</v>
+      </c>
       <c r="G8" s="13" t="n"/>
       <c r="H8" s="13">
         <f>SUM(F8:G8)</f>
@@ -2460,7 +2466,7 @@
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>2025 계약 77건 + 바이오힐보 US 68건 · 정산은 26년 발행</t>
+          <t>2025 계약 77건 + 바이오힐보 US 68건</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2521,9 @@
         <f>SUM(B10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="13" t="n"/>
+      <c r="F10" s="13" t="n">
+        <v>11760000</v>
+      </c>
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="13">
         <f>SUM(F10:G10)</f>
@@ -2530,11 +2538,7 @@
         <f>IFERROR(K10/J10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>정산은 26년 발행</t>
-        </is>
-      </c>
+      <c r="M10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -2551,7 +2555,9 @@
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="13" t="n"/>
+      <c r="F11" s="13" t="n">
+        <v>8190000</v>
+      </c>
       <c r="G11" s="13" t="n"/>
       <c r="H11" s="13">
         <f>SUM(F11:G11)</f>
@@ -2566,11 +2572,7 @@
         <f>IFERROR(K11/J11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>정산은 26년 발행</t>
-        </is>
-      </c>
+      <c r="M11" s="16" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -2619,7 +2621,9 @@
         <f>SUM(B13:D13)</f>
         <v/>
       </c>
-      <c r="F13" s="13" t="n"/>
+      <c r="F13" s="13" t="n">
+        <v>1050000</v>
+      </c>
       <c r="G13" s="13" t="n"/>
       <c r="H13" s="13">
         <f>SUM(F13:G13)</f>
@@ -2638,11 +2642,7 @@
         <f>IFERROR(K13/J13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>정산은 26.02 이후 발행</t>
-        </is>
-      </c>
+      <c r="M13" s="16" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>(발행월 미확정)</t>
+          <t>(국가 재배분)</t>
         </is>
       </c>
       <c r="B21" s="13" t="n"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="M21" s="16" t="inlineStr">
         <is>
-          <t>바이오힐보 US 30,000,000 국가 재배분 (금액 총계 불변)</t>
+          <t>바이오힐보 US 30,000,000 · 2025 계약 금액에 포함되어 있어 KR→글로벌 이동 (총계 불변)</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>금액 849,418,264 = 발행 확정 840,514,264 + JP 미발행 8,904,000</t>
+          <t>금액 909,248,264 = 발행 확정 900,344,264 + JP 미발행 8,904,000</t>
         </is>
       </c>
     </row>
@@ -3084,14 +3084,14 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>· 26.02~08 월별 금액은 26.09.07 확정 총액표를 그대로 반영했고, 이 7개월분이 세금계산서 발행액 전부다. 2025 진행분 정산·바이오힐보 US도 이 안에 포함된다.</t>
+          <t>· 26.02~08 월별 금액은 26.09.07 확정 총액표 그대로다. 여기에 2025 발행분 59,830,000(25.04~26.01 진행분 정산)을 더한 900,344,264원이 총 발행액이다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>· 바이오힐보 US 30,000,000원은 발행월이 특정되지 않아 국가 배분만 별도 행으로 조정했다(KR −30,000,000 / 글로벌 +30,000,000, 총계 불변).</t>
+          <t>· 바이오힐보 US 30,000,000원은 2025 계약 금액 안에 있어 국가 배분만 별도 행으로 조정했다(KR −30,000,000 / 글로벌 +30,000,000, 총계 불변).</t>
         </is>
       </c>
     </row>
@@ -4188,16 +4188,16 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>840514264</v>
+        <v>900344264</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>26.02~08 발행분이 전부. 2025 진행분 정산 59,830,000 · 바이오힐보 US 30,000,000도 이 안에 포함</t>
+          <t>26.02~08 확정 840,514,264 + 25년 발행 59,830,000 (바이오힐보 US 30,000,000 포함)</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>— 아래 참조</t>
+          <t>420,918원 ≠ 건당단가</t>
         </is>
       </c>
     </row>
@@ -4208,11 +4208,11 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-90773811</v>
+        <v>-30943811</v>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>기존 931,288,075은 25년 발행분 89,830,000을 별도로 더한 값 → 확정 총액에 이미 포함되어 있어 중복</t>
+          <t>기존 931,288,075은 US 30,000,000을 25년 발행분과 별도로 더한 값 → 중복. 여기에 26년 확정 −943,811 반영</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr"/>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>849418264</v>
+        <v>909248264</v>
       </c>
       <c r="C16" s="16" t="inlineStr"/>
       <c r="D16" s="16" t="inlineStr"/>
@@ -4284,7 +4284,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>③ 건당 청구단가 307,481원 — 산정 근거</t>
+          <t>③ 건당 청구단가 290,531원 — 산정 근거</t>
         </is>
       </c>
     </row>
@@ -4364,14 +4364,14 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>바이오힐보 US</t>
+          <t>2025 시딩 계약 + 바이오힐보 US</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>68</v>
+        <v>340</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>30000000</v>
+        <v>59830000</v>
       </c>
       <c r="D25" s="13">
         <f>IFERROR(C25/B25,"")</f>
@@ -4379,66 +4379,56 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>2025 시딩 계약</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>272</v>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>59830000</v>
-      </c>
-      <c r="D26" s="13">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>가중평균</t>
+        </is>
+      </c>
+      <c r="B26" s="18">
+        <f>SUM(B22:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="18">
+        <f>SUM(C22:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="18">
         <f>IFERROR(C26/B26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>가중평균</t>
-        </is>
-      </c>
-      <c r="B27" s="18">
-        <f>SUM(B22:B26)</f>
-        <v/>
-      </c>
-      <c r="C27" s="18">
-        <f>SUM(C22:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f>IFERROR(C27/B27,"")</f>
-        <v/>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>· 분자·분모가 같은 자료에서 함께 확정되는 항목만 사용 (전체 청구액의 57%, 진행 1,770건).</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>· 분자·분모가 같은 자료에서 함께 확정되는 항목만 사용 (전체 청구액의 65%, 진행 1,770건).</t>
+          <t>· 검증 1 — 아포맨 대조표 296,750,000 + 지급대행 5,000,000 = 세금계산서 발행 2~7월 301,750,000 (일치).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>· 검증 1 — 아포맨 대조표 296,750,000 + 지급대행 5,000,000 = 세금계산서 발행 2~7월 301,750,000 (일치).</t>
+          <t>· 검증 2 — 아포맨 원고료 272,248원 × 마크업 1.25 = 340,310원 = 실제 청구 단가 (일치).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>· 검증 2 — 아포맨 원고료 272,248원 × 마크업 1.25 = 340,310원 = 실제 청구 단가 (일치).</t>
+          <t>· 총액 900,344,264 ÷ 2,139 = 420,918원은 건당 단가가 아니다. 분자에 비시딩 항목이 있고, 청구 대응 진행 건수(약 2,787건)가 분모보다 크다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>· 총액 840,514,264 ÷ 2,139 = 392,948원은 건당 단가가 아니다. 분자에 비시딩 항목이 있고, 청구 대응 진행 건수(약 2,787건)가 분모보다 크다.</t>
+          <t>· 2025 계약 59,830,000원에 바이오힐보 US 30,000,000원이 포함되므로 국내 272건에 대응하는 금액은 29,830,000원(건당 109,669원)이 된다. 나노 단가(25만원)보다 낮아 272건 중 일부는 무상·재사용 건일 가능성이 있다 → A4 확인 항목.</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5168,24 +5158,24 @@
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>세금계산서 총액 (발행 확정)</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>26.02~08</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026.02~08 발행 확정</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>구분 없음</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13">
         <f>J6</f>
         <v/>
       </c>
@@ -5193,12 +5183,12 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  글로벌 · 일본(JP) 발행분</t>
+          <t>25.04~26.01  2025 발행분 (272건 + US 68건)</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>일본(JP)</t>
+          <t>국내+US</t>
         </is>
       </c>
       <c r="C26" s="13" t="n"/>
@@ -5209,63 +5199,59 @@
       <c r="H26" s="13" t="n"/>
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="13" t="n">
+        <v>59830000</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>세금계산서 총액 (발행 확정)</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18">
+        <f>J25+J26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  글로벌 · 일본(JP) 발행분</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>일본(JP)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n">
         <v>31796000</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  글로벌 · 바이오힐보 US</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>미국(US)</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n">
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  국내 (KR) = 총액 − 글로벌</t>
-        </is>
-      </c>
-      <c r="B28" s="37" t="inlineStr">
-        <is>
-          <t>국내</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="32" t="n"/>
-      <c r="G28" s="32" t="n"/>
-      <c r="H28" s="32" t="n"/>
-      <c r="I28" s="32" t="n"/>
-      <c r="J28" s="32">
-        <f>J25-J26-J27</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  + JP 미발행 (26.09)</t>
+          <t xml:space="preserve">  글로벌 · 바이오힐보 US (25년 발행분에 포함)</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>일본(JP)</t>
+          <t>미국(US)</t>
         </is>
       </c>
       <c r="C29" s="13" t="n"/>
@@ -5276,58 +5262,103 @@
       <c r="H29" s="13" t="n"/>
       <c r="I29" s="13" t="n"/>
       <c r="J29" s="13" t="n">
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  국내 (KR) = 총액 − 글로벌</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="32" t="n"/>
+      <c r="H30" s="32" t="n"/>
+      <c r="I30" s="32" t="n"/>
+      <c r="J30" s="32">
+        <f>J27-J28-J29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + JP 미발행 (26.09)</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>일본(JP)</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n">
         <v>8904000</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>진행 기준 총계</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n"/>
-      <c r="G30" s="18" t="n"/>
-      <c r="H30" s="18" t="n"/>
-      <c r="I30" s="18" t="n"/>
-      <c r="J30" s="18">
-        <f>J25+J29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>· 26.02~08 확정 총액 840,514,264원이 세금계산서 발행액 전부다. 2025 진행분 정산(59,830,000)과 바이오힐보 US(30,000,000)도 이 안에 포함되어 있어 별도로 더하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>· 기존 집계 931,288,075원은 위 두 항목을 확정 총액에 다시 더한 값이었다 (중복 89,830,000). 정정 후 −90,773,811원.</t>
-        </is>
+      <c r="B32" s="20" t="inlineStr"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18">
+        <f>J27+J31</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>· 확정 반영으로 빠진 것 — 26.02 아이디얼포맨 계상분 71,375,000원 (확정 2월 92,750,000원은 루테카 단독과 일치).</t>
+          <t>· 총 발행액 900,344,264원 = 26.02~08 확정 840,514,264 + 25년 발행 59,830,000. 25년 발행분 안에 바이오힐보 US 30,000,000원이 포함되어 있다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>· 프로젝트별 내역(②) 대비 차액 70,431,189원 — 2025 계약 정산분·US 청구분(합 89,830,000)의 일부가 여기에, 나머지는 이미 ②의 프로젝트 라인에 계상된 것으로 보인다. 정확한 귀속은 확인 필요.</t>
+          <t>· 기존 집계 931,288,075원은 US 30,000,000원을 25년 발행분과 별도로 한 번 더 더한 값이었다 → 중복 30,000,000. 여기에 26년 확정 −943,811을 반영해 순 −30,943,811원.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>· 확정 반영으로 빠진 것 — 26.02 아이디얼포맨 계상분 71,375,000원 (확정 2월 92,750,000원은 루테카 단독과 일치).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>· 확정 반영으로 더해진 것 — 26.03 +42,075,000 / 26.04 +5,058,689 / 26.05 +22,553,250 / 26.08 +31,740,500, 26.07 −30,996,250 (7→8월 발행 이동 추정) → 순 +70,431,189. 프로젝트별 귀속은 확인 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>· 총액표에 국가 구분이 없어 글로벌 시딩 라인 자료로 귀속했다. 루테카·바이오힐보는 분리 근거가 없어 혼재로 둔다.</t>
         </is>
@@ -7036,7 +7067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7098,7 +7129,7 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>발행 확정 총액이 프로젝트별 내역보다 70,431,189원 많다(US 30,000,000 제외 시 40,431,189). 2025 계약 정산분·US 청구분 포함 여부와 프로젝트별 귀속 확인 필요</t>
+          <t>26.02~08 발행 확정액이 프로젝트별 내역보다 70,431,189원 많다(03 +42,075,000 / 04 +5,058,689 / 05 +22,553,250 / 07 −30,996,250 / 08 +31,740,500). 프로젝트별 귀속 필요</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
@@ -7112,19 +7143,21 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>청구 대응 진행 건수</t>
+          <t>2025 계약 국내 건당액</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>세금계산서에 수량 미기재 → 840,514,264원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="n"/>
+          <t>59,830,000원에 US 30,000,000원이 포함되므로 국내 272건 대응액은 29,830,000원(건당 109,669원). 나노 단가 25만원보다 낮아 272건 중 무상·재사용 건 포함 여부 확인 필요</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>29830000</v>
+      </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
           <t>높음</t>
@@ -7133,16 +7166,16 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>IMD 국가 분류 오류</t>
+          <t>청구 대응 진행 건수</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>IMD는 일본 24건(WM 9·CG 8·BOH 7)만 분류하나 실제 99건. 54건(WM 30·CG 24)이 국내로 오분류</t>
+          <t>세금계산서에 수량 미기재 → 900,344,264원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
@@ -7154,16 +7187,16 @@
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보 국내 비용 귀속</t>
+          <t>IMD 국가 분류 오류</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>국내 195건·원고료 37,900,000인데 26년 발행액은 6,687,500뿐. 2025 계약 + 브랜드사 직계약으로 분산 추정</t>
+          <t>IMD는 일본 24건(WM 9·CG 8·BOH 7)만 분류하나 실제 99건. 54건(WM 30·CG 24)이 국내로 오분류</t>
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
@@ -7175,21 +7208,19 @@
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>식물나라 소계 오류</t>
+          <t>바이오힐보 국내 비용 귀속</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>원본 대조표 소계(384건 / 68,177,200 / 95,145,250)가 구버전(370건) 값. 재계산 시 87,676,850 / 106,723,250</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>11578000</v>
-      </c>
+          <t>국내 195건·원고료 37,900,000인데 26년 발행액은 6,687,500뿐. 2025 계약 + 브랜드사 직계약으로 분산 추정</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n"/>
       <c r="E9" s="16" t="inlineStr">
         <is>
           <t>높음</t>
@@ -7198,20 +7229,20 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>아포맨 누계 행 상충</t>
+          <t>식물나라 소계 오류</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>요약 행에 194,450,000 / 308,887,500 / 243,062,500 세 값 동시 기재. 월별 상세(237,400,000 / 296,750,000)가 정답</t>
+          <t>원본 대조표 소계(384건 / 68,177,200 / 95,145,250)가 구버전(370건) 값. 재계산 시 87,676,850 / 106,723,250</t>
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>12137500</v>
+        <v>11578000</v>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
@@ -7221,43 +7252,43 @@
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>JP 마크업률 미확정</t>
+          <t>아포맨 누계 행 상충</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>JP 고정비 29,465,000만 글로벌로 귀속. 세금계산서 42,292,500과의 차액 약 12.8백만(마크업·VAT)은 KR에 잔류</t>
+          <t>요약 행에 194,450,000 / 308,887,500 / 243,062,500 세 값 동시 기재. 월별 상세(237,400,000 / 296,750,000)가 정답</t>
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>12827500</v>
+        <v>12137500</v>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>높음</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>색조 3사 국내분 미발행</t>
+          <t>JP 마크업률 미확정</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>WM 국내 70건·CG 45건·FM 27건의 국내 시딩 비용이 26년 발행액에 없음. 하반기 계약으로 26.09 이후 발행 예정인지 확인</t>
+          <t>JP 고정비 29,465,000만 글로벌로 귀속. 세금계산서 42,292,500과의 차액 약 12.8백만(마크업·VAT)은 KR에 잔류</t>
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>34300000</v>
+        <v>12827500</v>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
@@ -7267,19 +7298,21 @@
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>비시딩 항목 전체 목록</t>
+          <t>색조 3사 국내분 미발행</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>지급대행·모션그래픽·솔루션 32,400,000원은 확인분만. 전체 목록 확보 시 건당 단가 정밀화</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="n"/>
+          <t>WM 국내 70건·CG 45건·FM 27건의 국내 시딩 비용이 26년 발행액에 없음. 하반기 계약으로 26.09 이후 발행 예정인지 확인</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>34300000</v>
+      </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
           <t>중</t>
@@ -7288,16 +7321,16 @@
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>2025년 상반기 데이터</t>
+          <t>비시딩 항목 전체 목록</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>IMD가 25.09.29부터라 25년 1~9월 업로드 데이터 없음. 2025 계약 272건 중 219건이 성과 집계 밖</t>
+          <t>지급대행·모션그래픽·솔루션 32,400,000원은 확인분만. 전체 목록 확보 시 건당 단가 정밀화</t>
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
@@ -7309,63 +7342,61 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>루테카 US 수량</t>
+          <t>2025년 상반기 데이터</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>US TikTok 약 20건이 IMD·세금계산서 어느 쪽에서도 특정되지 않아 집계 제외</t>
+          <t>IMD가 25.09.29부터라 25년 1~9월 업로드 데이터 없음. 2025 계약 272건 중 219건이 성과 집계 밖</t>
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>중</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보 US 미집계 32건</t>
+          <t>루테카 US 수량</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>US 68건 중 36건만 성과 확보(4,739,117뷰). 나머지 32건 조회수·참여 데이터 미확보 → 실제 성과는 현재 수치 이상</t>
+          <t>US TikTok 약 20건이 IMD·세금계산서 어느 쪽에서도 특정되지 않아 집계 제외</t>
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>낮음</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보 US 원고료</t>
+          <t>바이오힐보 US 미집계 32건</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>US 36건 원고료 미기재. 청구 30,000,000원만 확인되어 CPV는 청구 기준으로 산출(국내·JP와 기준 상이)</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>30000000</v>
-      </c>
+          <t>US 68건 중 36건만 성과 확보(4,739,117뷰). 나머지 32건 조회수·참여 데이터 미확보 → 실제 성과는 현재 수치 이상</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n"/>
       <c r="E17" s="16" t="inlineStr">
         <is>
           <t>중</t>
@@ -7374,47 +7405,47 @@
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>바이오힐보 US 원고료</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>US 36건 원고료 미기재. 청구 30,000,000원만 확인되어 CPV는 청구 기준으로 산출(국내·JP와 기준 상이)</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>케어플러스 청구 차이</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>협의 비용 합 7,825,000(+VAT 8,607,500) vs 세금계산서 8,998,750 → 391,250 차이</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D19" s="13" t="n">
         <v>391250</v>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>낮음</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>해결</t>
-        </is>
-      </c>
-      <c r="B19" s="38" t="inlineStr">
-        <is>
-          <t>루테카 발행액 71,375,000</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>26.02 확정액이 92,750,000(루테카 단독)으로 확정되어 아이디얼포맨 2월 계상분 71,375,000은 제외 확정</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
         </is>
       </c>
     </row>
@@ -7426,12 +7457,12 @@
       </c>
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>케어플러스 원고료</t>
+          <t>루테카 발행액 71,375,000</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>시딩현황에서 확인 — 마이크로 5건×200,000 + 나노 27건×100,000 = 3,700,000원. CPV 19.63원 / CPE 2,012원</t>
+          <t>26.02 확정액이 92,750,000(루테카 단독)으로 확정되어 아이디얼포맨 2월 계상분 71,375,000은 제외 확정</t>
         </is>
       </c>
       <c r="D20" s="27" t="n"/>
@@ -7449,12 +7480,12 @@
       </c>
       <c r="B21" s="38" t="inlineStr">
         <is>
-          <t>바이오힐보 US 성과</t>
+          <t>케어플러스 원고료</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>IMD 26.09.07로 36건 확보 — 4,739,117뷰 / 좋아요 23,068 / 댓글 1,066 / 최대 2,954,129뷰(전체 1위)</t>
+          <t>시딩현황에서 확인 — 마이크로 5건×200,000 + 나노 27건×100,000 = 3,700,000원. CPV 19.63원 / CPE 2,012원</t>
         </is>
       </c>
       <c r="D21" s="27" t="n"/>
@@ -7464,8 +7495,31 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>해결</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>바이오힐보 US 성과</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>IMD 26.09.07로 36건 확보 — 4,739,117뷰 / 좋아요 23,068 / 댓글 1,066 / 최대 2,954,129뷰(전체 1위)</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>· 금액 영향은 미설명·수정 필요 금액의 절대값이며 서로 중복될 수 있어 합산하지 않는다.</t>
         </is>

--- a/reports/올리브영_시딩_성과보고서.xlsx
+++ b/reports/올리브영_시딩_성과보고서.xlsx
@@ -4428,7 +4428,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>· 2025 계약 59,830,000원에 바이오힐보 US 30,000,000원이 포함되므로 국내 272건에 대응하는 금액은 29,830,000원(건당 109,669원)이 된다. 나노 단가(25만원)보다 낮아 272건 중 일부는 무상·재사용 건일 가능성이 있다 → A4 확인 항목.</t>
+          <t>· 2025 계약 59,830,000원에 바이오힐보 US 30,000,000원이 포함되어 국내 272건 대응액은 29,830,000원(건당 109,669원)이다. 272건에 무상건·소액건이 섞여 있어 나온 정상 단가이며 오류가 아니다.</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>자료 간 불일치 · 미확정 사항 12건 (해결 3건 포함) · 26.09.07 갱신</t>
+          <t>자료 간 불일치 · 미확정 사항 · 해결·확정 4건 포함 · 26.09.07 갱신</t>
         </is>
       </c>
     </row>
@@ -7143,21 +7143,19 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>2025 계약 국내 건당액</t>
+          <t>청구 대응 진행 건수</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>59,830,000원에 US 30,000,000원이 포함되므로 국내 272건 대응액은 29,830,000원(건당 109,669원). 나노 단가 25만원보다 낮아 272건 중 무상·재사용 건 포함 여부 확인 필요</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>29830000</v>
-      </c>
+          <t>세금계산서에 수량 미기재 → 900,344,264원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n"/>
       <c r="E6" s="16" t="inlineStr">
         <is>
           <t>높음</t>
@@ -7166,16 +7164,16 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>청구 대응 진행 건수</t>
+          <t>IMD 국가 분류 오류</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>세금계산서에 수량 미기재 → 900,344,264원에 대응하는 진행 건수 확정 불가(추정 약 2,787건). 확정 시 건당 단가 확정 가능</t>
+          <t>IMD는 일본 24건(WM 9·CG 8·BOH 7)만 분류하나 실제 99건. 54건(WM 30·CG 24)이 국내로 오분류</t>
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
@@ -7187,16 +7185,16 @@
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>IMD 국가 분류 오류</t>
+          <t>바이오힐보 국내 비용 귀속</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>IMD는 일본 24건(WM 9·CG 8·BOH 7)만 분류하나 실제 99건. 54건(WM 30·CG 24)이 국내로 오분류</t>
+          <t>국내 195건·원고료 37,900,000인데 26년 발행액은 6,687,500뿐. 2025 계약 + 브랜드사 직계약으로 분산 추정</t>
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
@@ -7208,19 +7206,21 @@
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보 국내 비용 귀속</t>
+          <t>식물나라 소계 오류</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>국내 195건·원고료 37,900,000인데 26년 발행액은 6,687,500뿐. 2025 계약 + 브랜드사 직계약으로 분산 추정</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="n"/>
+          <t>원본 대조표 소계(384건 / 68,177,200 / 95,145,250)가 구버전(370건) 값. 재계산 시 87,676,850 / 106,723,250</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>11578000</v>
+      </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
           <t>높음</t>
@@ -7229,20 +7229,20 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>식물나라 소계 오류</t>
+          <t>아포맨 누계 행 상충</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>원본 대조표 소계(384건 / 68,177,200 / 95,145,250)가 구버전(370건) 값. 재계산 시 87,676,850 / 106,723,250</t>
+          <t>요약 행에 194,450,000 / 308,887,500 / 243,062,500 세 값 동시 기재. 월별 상세(237,400,000 / 296,750,000)가 정답</t>
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>11578000</v>
+        <v>12137500</v>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
@@ -7252,43 +7252,43 @@
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>아포맨 누계 행 상충</t>
+          <t>JP 마크업률 미확정</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>요약 행에 194,450,000 / 308,887,500 / 243,062,500 세 값 동시 기재. 월별 상세(237,400,000 / 296,750,000)가 정답</t>
+          <t>JP 고정비 29,465,000만 글로벌로 귀속. 세금계산서 42,292,500과의 차액 약 12.8백만(마크업·VAT)은 KR에 잔류</t>
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>12137500</v>
+        <v>12827500</v>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>JP 마크업률 미확정</t>
+          <t>색조 3사 국내분 미발행</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>JP 고정비 29,465,000만 글로벌로 귀속. 세금계산서 42,292,500과의 차액 약 12.8백만(마크업·VAT)은 KR에 잔류</t>
+          <t>WM 국내 70건·CG 45건·FM 27건의 국내 시딩 비용이 26년 발행액에 없음. 하반기 계약으로 26.09 이후 발행 예정인지 확인</t>
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>12827500</v>
+        <v>34300000</v>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
@@ -7298,21 +7298,19 @@
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>색조 3사 국내분 미발행</t>
+          <t>비시딩 항목 전체 목록</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>WM 국내 70건·CG 45건·FM 27건의 국내 시딩 비용이 26년 발행액에 없음. 하반기 계약으로 26.09 이후 발행 예정인지 확인</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>34300000</v>
-      </c>
+          <t>지급대행·모션그래픽·솔루션 32,400,000원은 확인분만. 전체 목록 확보 시 건당 단가 정밀화</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n"/>
       <c r="E13" s="16" t="inlineStr">
         <is>
           <t>중</t>
@@ -7321,16 +7319,16 @@
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>비시딩 항목 전체 목록</t>
+          <t>2025년 상반기 데이터</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>지급대행·모션그래픽·솔루션 32,400,000원은 확인분만. 전체 목록 확보 시 건당 단가 정밀화</t>
+          <t>IMD가 25.09.29부터라 25년 1~9월 업로드 데이터 없음. 2025 계약 272건 중 219건이 성과 집계 밖</t>
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
@@ -7342,61 +7340,63 @@
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>2025년 상반기 데이터</t>
+          <t>루테카 US 수량</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>IMD가 25.09.29부터라 25년 1~9월 업로드 데이터 없음. 2025 계약 272건 중 219건이 성과 집계 밖</t>
+          <t>US TikTok 약 20건이 IMD·세금계산서 어느 쪽에서도 특정되지 않아 집계 제외</t>
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>낮음</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>루테카 US 수량</t>
+          <t>바이오힐보 US 미집계 32건</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>US TikTok 약 20건이 IMD·세금계산서 어느 쪽에서도 특정되지 않아 집계 제외</t>
+          <t>US 68건 중 36건만 성과 확보(4,739,117뷰). 나머지 32건 조회수·참여 데이터 미확보 → 실제 성과는 현재 수치 이상</t>
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>중</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보 US 미집계 32건</t>
+          <t>바이오힐보 US 원고료</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>US 68건 중 36건만 성과 확보(4,739,117뷰). 나머지 32건 조회수·참여 데이터 미확보 → 실제 성과는 현재 수치 이상</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="n"/>
+          <t>US 36건 원고료 미기재. 청구 30,000,000원만 확인되어 CPV는 청구 기준으로 산출(국내·JP와 기준 상이)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>30000000</v>
+      </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
           <t>중</t>
@@ -7405,47 +7405,47 @@
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>바이오힐보 US 원고료</t>
+          <t>케어플러스 청구 차이</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>US 36건 원고료 미기재. 청구 30,000,000원만 확인되어 CPV는 청구 기준으로 산출(국내·JP와 기준 상이)</t>
+          <t>협의 비용 합 7,825,000(+VAT 8,607,500) vs 세금계산서 8,998,750 → 391,250 차이</t>
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>30000000</v>
+        <v>391250</v>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>낮음</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>케어플러스 청구 차이</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>협의 비용 합 7,825,000(+VAT 8,607,500) vs 세금계산서 8,998,750 → 391,250 차이</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>391250</v>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>낮음</t>
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>해결</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>루테카 발행액 71,375,000</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>26.02 확정액이 92,750,000(루테카 단독)으로 확정되어 아이디얼포맨 2월 계상분 71,375,000은 제외 확정</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7457,12 @@
       </c>
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>루테카 발행액 71,375,000</t>
+          <t>케어플러스 원고료</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>26.02 확정액이 92,750,000(루테카 단독)으로 확정되어 아이디얼포맨 2월 계상분 71,375,000은 제외 확정</t>
+          <t>시딩현황에서 확인 — 마이크로 5건×200,000 + 나노 27건×100,000 = 3,700,000원. CPV 19.63원 / CPE 2,012원</t>
         </is>
       </c>
       <c r="D20" s="27" t="n"/>
@@ -7475,17 +7475,17 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>해결</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="B21" s="38" t="inlineStr">
         <is>
-          <t>케어플러스 원고료</t>
+          <t>2025 계약 국내 건당액</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>시딩현황에서 확인 — 마이크로 5건×200,000 + 나노 27건×100,000 = 3,700,000원. CPV 19.63원 / CPE 2,012원</t>
+          <t>59,830,000원에 US 30,000,000원이 포함되어 국내 272건 대응액은 29,830,000원(건당 109,669원). 272건에 무상건·소액건이 섞여 있어 이 단가가 정상 — 오류 아님</t>
         </is>
       </c>
       <c r="D21" s="27" t="n"/>
